--- a/backend/uploads/qa_generated/69A_ST_TC_v13__2__484db480.xlsx
+++ b/backend/uploads/qa_generated/69A_ST_TC_v13__2__484db480.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,8 +34,25 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Browallia New"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="26"/>
+    </font>
+    <font>
+      <name val="Browallia New"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Browallia New"/>
+      <color rgb="00000000"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -54,8 +71,20 @@
         <bgColor rgb="00F1F5F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CDEEFF"/>
+        <bgColor rgb="00CDEEFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -77,11 +106,149 @@
         <color rgb="00CBD5E1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+    </border>
+    <border/>
+    <border>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0C4DE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0C4DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0C4DE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0C4DE"/>
+      </bottom>
+    </border>
+    <border>
+      <right/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -99,6 +266,90 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,444 +715,321 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SPECTRA QA PLATFORM - 69A_ST_TC_v13 (2) (Test Case)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Project Name / โครงการ :</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>TIFFA-RGP (69A)</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Create Date / วันที่ :</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="7" t="n"/>
+      <c r="D1" s="7" t="n"/>
+      <c r="E1" s="7" t="n"/>
+      <c r="F1" s="7" t="n"/>
+      <c r="G1" s="7" t="n"/>
+      <c r="H1" s="7" t="n"/>
+      <c r="I1" s="7" t="n"/>
+      <c r="J1" s="7" t="n"/>
+      <c r="K1" s="7" t="n"/>
+      <c r="L1" s="7" t="n"/>
+      <c r="M1" s="7" t="n"/>
+      <c r="N1" s="7" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
+      <c r="J2" s="7" t="n"/>
+      <c r="K2" s="7" t="n"/>
+      <c r="L2" s="7" t="n"/>
+      <c r="M2" s="7" t="n"/>
+      <c r="N2" s="7" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="7" t="n"/>
+      <c r="I3" s="7" t="n"/>
+      <c r="J3" s="7" t="n"/>
+      <c r="K3" s="7" t="n"/>
+      <c r="L3" s="7" t="n"/>
+      <c r="M3" s="7" t="n"/>
+      <c r="N3" s="7" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
+      <c r="J4" s="7" t="n"/>
+      <c r="K4" s="7" t="n"/>
+      <c r="L4" s="7" t="n"/>
+      <c r="M4" s="7" t="n"/>
+      <c r="N4" s="7" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="37" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="9" t="n"/>
+      <c r="I5" s="9" t="n"/>
+      <c r="J5" s="9" t="n"/>
+      <c r="K5" s="9" t="n"/>
+      <c r="L5" s="9" t="n"/>
+      <c r="M5" s="9" t="n"/>
+      <c r="N5" s="11" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="B6" s="12" t="n"/>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Project Name :</t>
+        </is>
+      </c>
+      <c r="D6" s="38" t="inlineStr">
+        <is>
+          <t>FoodSmile</t>
+        </is>
+      </c>
+      <c r="E6" s="38" t="n"/>
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>Create Date :</t>
+        </is>
+      </c>
+      <c r="H6" s="39" t="n"/>
+      <c r="I6" s="38" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-      <c r="H3" s="3" t="n"/>
-    </row>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Module / ฟังก์ชัน :</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>ระบบจัดการใบอนุญาตและการส่งออก (Permit Management)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Test Engine / เครื่องมือ :</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Spectra AI (Gemini 3.1 Pro)</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="n"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Tester / ผู้จัดทำ :</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Status / สถานะ :</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Baseline Specification</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="n"/>
-    </row>
-    <row r="8" ht="28" customHeight="1">
+      <c r="J6" s="38" t="n"/>
+      <c r="K6" s="38" t="n"/>
+      <c r="L6" s="38" t="n"/>
+      <c r="M6" s="38" t="n"/>
+      <c r="N6" s="17" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="B7" s="12" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
+      <c r="G7" s="16" t="n"/>
+      <c r="H7" s="16" t="n"/>
+      <c r="I7" s="16" t="n"/>
+      <c r="J7" s="16" t="n"/>
+      <c r="K7" s="16" t="n"/>
+      <c r="L7" s="16" t="n"/>
+      <c r="M7" s="16" t="n"/>
+      <c r="N7" s="17" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Test Objective
-(วัตถุประสงค์การทดสอบ)</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Test Description / Procedure
-(ขั้นตอนการทดสอบ)</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Project ID:</t>
+        </is>
+      </c>
+      <c r="D8" s="38" t="inlineStr">
         <is>
           <t>Test Data
 (ข้อมูลทดสอบ)</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Expected Result
-(ผลลัพธ์ที่คาดหวัง)</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Actual Result
-(ผลการทดสอบจริง)</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="E8" s="38" t="n"/>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Start Test Date :</t>
+        </is>
+      </c>
+      <c r="H8" s="39" t="n"/>
+      <c r="I8" s="38" t="inlineStr">
         <is>
           <t>Result (Pass/Fail)</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Req No.
-(รหัสข้อกำหนด)</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>Updated By
-(ผู้ทดสอบ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+      <c r="J8" s="38" t="n"/>
+      <c r="K8" s="38" t="n"/>
+      <c r="L8" s="38" t="n"/>
+      <c r="M8" s="38" t="n"/>
+      <c r="N8" s="17" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>69AA1001</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>ตรวจสอบว่าผู้ใช้สามารถสร้างเอกสารใบอนุญาตฉบับร่าง (Draft LPI) จากหน้าใบแจ้งหนี้ (Invoice) โดยกดปุ่มขอใบอนุญาตได้สำเร็จ</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>กลุ่มผู้ใช้ (Actor): ผู้ใช้งานระบบ (User)
-เงื่อนไขก่อนหน้า (Pre-conditions): ผู้ใช้เข้าสู่ระบบและมีสิทธิ์ใช้งานเมนูขอใบอนุญาต
-เงื่อนไขหลังการทำงาน (Post-conditions): ระบบสร้างเอกสาร LPI และจัดกลุ่มหน่วยงานอัตโนมัติ
-ขั้นตอนการทำงานปกติ (Main Path):
-1. ไปที่เมนูจัดการใบแจ้งหนี้ (Invoice Menu)
-2. สร้างใบแจ้งหนี้ที่มีสินค้ารหัสพิกัดศุลกากร (HS Code) ควบคุมโดย อย.
-3. คลิกปุ่ม 'ขอใบอนุญาต (Create LPI)' ในหน้าใบแจ้งหนี้
-4. ตรวจสอบผลลัพธ์ในหน้าจัดการใบอนุญาต (Permit)
-ขั้นตอนกรณีเกิดข้อผิดพลาด (Unhappy Path):
-1. หากระบบไม่สามารถเชื่อมต่อฐานข้อมูลได้ ให้แสดงข้อความแจ้งเตือน 'ไม่สามารถสร้างใบอนุญาตได้ กรุณาลองใหม่อีกครั้ง'
-เกณฑ์การยอมรับ (Acceptance Criteria):
-- Given ผู้ใช้อยู่หน้าใบแจ้งหนี้ที่มีสินค้าควบคุม When ผู้ใช้คลิกปุ่มขอใบอนุญาต Then ระบบสร้างเอกสาร LPI สถานะ 'ฉบับร่าง (Draft)' สีเทา และจัดกลุ่มเข้าหน่วยงาน อย. อัตโนมัติ</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>ข้อมูลใบแจ้งหนี้ (Invoice): สินค้าที่มีรหัสพิกัดศุลกากร (HS Code) ควบคุมโดย อย. จำนวน 1 รายการ</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>ระบบสร้างเอกสาร LPI สำเร็จ แสดงสถานะเป็น 'ฉบับร่าง (Draft)' สีเทา และจัดกลุ่มเข้าหน่วยงาน อย. อัตโนมัติ พร้อมแสดงข้อความบันทึกสำเร็จ</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="16" t="n"/>
+      <c r="G9" s="16" t="n"/>
+      <c r="H9" s="16" t="n"/>
+      <c r="I9" s="16" t="n"/>
+      <c r="J9" s="16" t="n"/>
+      <c r="K9" s="16" t="n"/>
+      <c r="L9" s="16" t="n"/>
+      <c r="M9" s="16" t="n"/>
+      <c r="N9" s="17" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>69AA1005</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Tester Name :</t>
+        </is>
+      </c>
+      <c r="D10" s="38" t="inlineStr">
+        <is>
+          <t>ข้อมูลใบแจ้งหนี้ (Invoice): สินค้าที่รหัสพิกัดศุลกากร (HS Code) ไม่อยู่ในตาราง Permission_Goods</t>
+        </is>
+      </c>
+      <c r="E10" s="38" t="n"/>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>Finish Test Date :</t>
+        </is>
+      </c>
+      <c r="H10" s="39" t="n"/>
+      <c r="I10" s="38" t="inlineStr">
         <is>
           <t>[-]</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>REQ0001</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>69AA1005</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>ตรวจสอบระบบป้องกันการสร้างใบอนุญาต (LPI) จากใบแจ้งหนี้ (Invoice) ที่ไม่มีสินค้าควบคุม</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>กลุ่มผู้ใช้ (Actor): ผู้ใช้งานระบบ (User)
-เงื่อนไขก่อนหน้า (Pre-conditions): ผู้ใช้เข้าสู่ระบบและอยู่ในหน้าจัดการใบแจ้งหนี้
-เงื่อนไขหลังการทำงาน (Post-conditions): ระบบไม่อนุญาตให้สร้าง LPI
-ขั้นตอนการทำงานปกติ (Main Path):
-1. สร้างใบแจ้งหนี้ที่สินค้าทุกรายการมีรหัสพิกัดศุลกากร (HS Code) ไม่อยู่ในตารางสินค้าควบคุม (Permission_Goods)
-2. ตรวจสอบสถานะของปุ่ม 'ขอใบอนุญาต (Create LPI)'
-ขั้นตอนกรณีเกิดข้อผิดพลาด (Unhappy Path):
-1. หากผู้ใช้พยายามบังคับกดปุ่มผ่านการแก้โค้ด (Inspect Element) ระบบต้องแสดงข้อความ 'ไม่อนุญาตให้ทำรายการ เนื่องจากไม่มีสินค้าควบคุม'
-เกณฑ์การยอมรับ (Acceptance Criteria):
-- Given ใบแจ้งหนี้ไม่มีสินค้าควบคุม When ผู้ใช้ตรวจสอบหน้าจอ Then ปุ่มขอใบอนุญาตจะถูกปิดการใช้งาน (Disable) และไม่แสดงรายการสินค้าให้เลือก</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>ข้อมูลใบแจ้งหนี้ (Invoice): สินค้าที่รหัสพิกัดศุลกากร (HS Code) ไม่อยู่ในตาราง Permission_Goods</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>ระบบไม่แสดงสินค้ารายการใดให้เลือกขอใบอนุญาต และปุ่ม 'ขอใบอนุญาต (Create LPI)' ถูกปิดการใช้งาน (Disable) อย่างถูกต้อง</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>REQ0001</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
+      <c r="J10" s="38" t="n"/>
+      <c r="K10" s="38" t="n"/>
+      <c r="L10" s="38" t="n"/>
+      <c r="M10" s="38" t="n"/>
+      <c r="N10" s="17" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>69AA1011</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>ตรวจสอบการแสดงผลสถานะใบอนุญาต (LPI) เป็น 'ส่งแล้ว (Sent)' เมื่อส่งคำขอสำเร็จ</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>กลุ่มผู้ใช้ (Actor): ผู้ใช้งานระบบ (User)
-เงื่อนไขก่อนหน้า (Pre-conditions): มีเอกสาร LPI สถานะฉบับร่างที่กรอกข้อมูลครบถ้วน
-เงื่อนไขหลังการทำงาน (Post-conditions): สถานะเอกสารเปลี่ยนเป็นส่งแล้ว
-ขั้นตอนการทำงานปกติ (Main Path):
-1. เปิดเอกสาร LPI ที่กรอกข้อมูลครบถ้วน
-2. คลิกปุ่ม 'ส่งคำขอ (Submit)' ไปยังหน่วยงาน (NSW)
-3. ตรวจสอบสถานะที่แสดงในหน้าจัดการใบอนุญาต
-ขั้นตอนกรณีเกิดข้อผิดพลาด (Unhappy Path):
-1. หากการส่งข้อมูลล้มเหลว ระบบต้องแสดงข้อความ 'การส่งข้อมูลผิดพลาด กรุณาตรวจสอบการเชื่อมต่อ'
-เกณฑ์การยอมรับ (Acceptance Criteria):
-- Given เอกสาร LPI พร้อมส่ง When ผู้ใช้กดส่งคำขอสำเร็จ Then ระบบแสดงสถานะเป็น 'ส่งแล้ว (Sent)'</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>เอกสาร LPI ที่กรอกข้อมูลบังคับครบถ้วนและพร้อมส่งไปยังหน่วยงาน</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>ระบบส่งข้อมูลสำเร็จและแสดงสถานะเอกสารเป็น 'ส่งแล้ว (Sent)' ถูกต้องตรงตามเงื่อนไข</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>REQ0003</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
+      <c r="G11" s="16" t="n"/>
+      <c r="H11" s="16" t="n"/>
+      <c r="I11" s="16" t="n"/>
+      <c r="J11" s="16" t="n"/>
+      <c r="K11" s="16" t="n"/>
+      <c r="L11" s="16" t="n"/>
+      <c r="M11" s="16" t="n"/>
+      <c r="N11" s="17" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>69AA1027</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>ตรวจสอบการยกเลิกคำขอใบอนุญาต (LPI) ที่มีสถานะ 'เสร็จสิ้น (Completed)'</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>กลุ่มผู้ใช้ (Actor): ผู้ใช้งานระบบ (User)
-เงื่อนไขก่อนหน้า (Pre-conditions): มีเอกสาร LPI สถานะเสร็จสิ้น และผูกกับใบขนที่ยังไม่ถึงสถานะชำระเงินสำเร็จ
-เงื่อนไขหลังการทำงาน (Post-conditions): เอกสาร LPI ถูกยกเลิกและเก็บประวัติผู้ยกเลิก
-ขั้นตอนการทำงานปกติ (Main Path):
-1. เปิดเอกสาร LPI ที่มีสถานะ 'เสร็จสิ้น (Completed)'
-2. คลิกปุ่ม 'ยกเลิกคำขอ (Cancel)'
-3. เลือกระบุเหตุผลการยกเลิกจาก 9 เหตุผลที่กำหนด
-4. ยืนยันการยกเลิก
-ขั้นตอนกรณีเกิดข้อผิดพลาด (Unhappy Path):
-1. หากไม่ได้เลือกเหตุผล ระบบจะแสดงข้อความ 'กรุณาระบุเหตุผลการยกเลิก'
-เกณฑ์การยอมรับ (Acceptance Criteria):
-- Given LPI สถานะเสร็จสิ้น When ผู้ใช้กดยกเลิกและระบุเหตุผล Then LPI เปลี่ยนสถานะเป็น 'ยกเลิก (Cancel)' และระบบแจ้งเตือนให้ขอใบอนุญาตใหม่</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Project Release / Version :</t>
+        </is>
+      </c>
+      <c r="D12" s="38" t="inlineStr">
         <is>
           <t>เอกสาร LPI สถานะเสร็จสิ้น 1 รายการ, เหตุผลการยกเลิก: 'ข้อมูลสินค้าผิดพลาด'</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>เอกสาร LPI เปลี่ยนเป็นสถานะ 'ยกเลิก (Cancel)' เลขที่ใบอนุญาตเดิมถูกลบออก ระบบแจ้งเตือนให้ขอใบอนุญาตใหม่อีกครั้ง และสถานะความพร้อมของใบขนกลับเป็น 'ยังไม่พร้อมส่ง'</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>REQ0009</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
+      <c r="E12" s="38" t="n"/>
+      <c r="F12" s="38" t="n"/>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Module / Function: </t>
+        </is>
+      </c>
+      <c r="H12" s="39" t="n"/>
+      <c r="I12" s="38" t="inlineStr">
+        <is>
+          <t>Test Cases</t>
+        </is>
+      </c>
+      <c r="J12" s="38" t="n"/>
+      <c r="K12" s="38" t="n"/>
+      <c r="L12" s="38" t="n"/>
+      <c r="M12" s="38" t="n"/>
+      <c r="N12" s="17" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>69AA1032</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>ตรวจสอบการจัดการใบอนุญาต (LPI) เมื่อใบขนสินค้าที่มีสถานะชำระเงินสำเร็จถูกยกเลิก</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>กลุ่มผู้ใช้ (Actor): ผู้ใช้งานระบบ (User)
-เงื่อนไขก่อนหน้า (Pre-conditions): LPI สถานะเสร็จสิ้น ผูกกับใบขนที่ชำระเงินสำเร็จแล้ว
-เงื่อนไขหลังการทำงาน (Post-conditions): ใบขนถูกยกเลิก แต่เลข LPI ยังคงอยู่และนำไปใช้ใหม่ได้
-ขั้นตอนการทำงานปกติ (Main Path):
-1. ค้นหาใบขนสินค้าที่มีสถานะชำระเงินสำเร็จและมี LPI ผูกอยู่
-2. ดำเนินการยกเลิกใบขนสินค้านั้น (Cancel Declaration)
-3. ตรวจสอบเลขที่ LPI ในประวัติใบขนที่ถูกยกเลิก
-4. นำเลขที่ LPI เดิมไปผูกกับใบขนสินค้าฉบับใหม่
-ขั้นตอนกรณีเกิดข้อผิดพลาด (Unhappy Path):
-1. หากระบบไม่สามารถปลดล็อค LPI ได้ ให้แสดงข้อความ 'เกิดข้อผิดพลาดในการคืนค่าใบอนุญาต'
-เกณฑ์การยอมรับ (Acceptance Criteria):
-- Given ใบขนชำระเงินสำเร็จถูกยกเลิก When ผู้ใช้ตรวจสอบ LPI Then เลข LPI ยังคงอยู่ในประวัติและสามารถนำไปผูกกับใบขนใหม่ได้</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>ใบขนสินค้าสถานะชำระเงินสำเร็จที่ถูกยกเลิก พร้อมเลขที่ LPI ที่ผูกอยู่</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>เลขที่ LPI ยังคงอยู่ในใบขนที่ถูกยกเลิกเพื่อเก็บเป็นประวัติ และระบบอนุญาตให้นำเลขที่ LPI เดิมไปใช้ผูกกับใบขนฉบับอื่นได้สำเร็จ</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>REQ0011</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
+      <c r="B13" s="40" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="26" t="n"/>
+      <c r="E13" s="26" t="n"/>
+      <c r="F13" s="26" t="n"/>
+      <c r="G13" s="26" t="n"/>
+      <c r="H13" s="26" t="n"/>
+      <c r="I13" s="26" t="n"/>
+      <c r="J13" s="26" t="n"/>
+      <c r="K13" s="26" t="n"/>
+      <c r="L13" s="26" t="n"/>
+      <c r="M13" s="26" t="n"/>
+      <c r="N13" s="27" t="n"/>
+    </row>
+    <row r="14" ht="14" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>69AA1061</t>
@@ -958,64 +1086,34 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="24" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>NFR-PERF-001</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>ตรวจสอบประสิทธิภาพ (Performance) การโหลดหน้าจอจัดการใบอนุญาต (Permit) เมื่อมีข้อมูลมากกว่า 100 รายการ</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>กลุ่มผู้ใช้ (Actor): ผู้ใช้งานระบบ (User)
-เงื่อนไขก่อนหน้า (Pre-conditions): ฐานข้อมูลมีเอกสาร LPI มากกว่า 100 รายการ
-เงื่อนไขหลังการทำงาน (Post-conditions): หน้าจอแสดงผลข้อมูลครบถ้วนภายในเวลาที่กำหนด
-ขั้นตอนการทำงานปกติ (Main Path):
-1. เข้าสู่ระบบด้วยบัญชีผู้ใช้งาน
-2. คลิกเมนู 'จัดการใบอนุญาต (Permit)'
-3. จับเวลาตั้งแต่เริ่มคลิกจนกระทั่งข้อมูลแสดงผลบนหน้าจอครบถ้วน
-ขั้นตอนกรณีเกิดข้อผิดพลาด (Unhappy Path):
-1. หากโหลดนานเกิน 3 วินาที ระบบต้องแสดงสถานะกำลังโหลด (Loading Spinner) และไม่ค้าง
-เกณฑ์การยอมรับ (Acceptance Criteria):
-- Given มีข้อมูล LPI &gt; 100 รายการ When ผู้ใช้เข้าสู่หน้าจอ Then ระบบต้องโหลดข้อมูลเสร็จสิ้นภายใน 3 วินาที</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>ฐานข้อมูลจำลองที่มีเอกสาร LPI จำนวน 150 รายการ</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>หน้าจอโหลดข้อมูลสำเร็จและแสดงผลครบถ้วนภายในเวลาไม่เกิน 3 วินาที โดยไม่มีข้อมูลตกหล่นหรือหน้าจอค้าง</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUNCTIONAL REQUIREMENTS (Requirements No.) :</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="n"/>
+      <c r="D15" s="30" t="n"/>
+      <c r="E15" s="31" t="inlineStr">
         <is>
           <t>[-]</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>NFR-PERF-001</t>
-        </is>
-      </c>
+      <c r="F15" s="32" t="n"/>
+      <c r="G15" s="32" t="n"/>
+      <c r="H15" s="33" t="n"/>
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>AI Agent</t>
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="12" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>NFR-SEC-001</t>
@@ -1071,74 +1169,90 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="32" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>NFR-REL-001</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>ตรวจสอบความน่าเชื่อถือและความพร้อมใช้งานของระบบ (Reliability &amp; Availability &gt;= 99.9%)</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>กลุ่มผู้ใช้ (Actor): ผู้ดูแลระบบ (System Admin)
-เงื่อนไขก่อนหน้า (Pre-conditions): ระบบทำงานบนเซิร์ฟเวอร์ทดสอบ (Test Environment)
-เงื่อนไขหลังการทำงาน (Post-conditions): ระบบสามารถทำงานต่อเนื่องหรือกู้คืนได้รวดเร็ว
-ขั้นตอนการทำงานปกติ (Main Path):
-1. จำลองสถานการณ์เซิร์ฟเวอร์ทำงานหนัก (Load Testing) เป็นเวลา 24 ชั่วโมง
-2. ตรวจสอบ Uptime ของระบบผ่านเครื่องมือ Monitoring
-ขั้นตอนกรณีเกิดข้อผิดพลาด (Unhappy Path):
-1. หาก Service บางตัวหยุดทำงาน (Crash) ระบบ Auto-scaling หรือ Auto-restart ต้องทำงานภายใน 1 นาที
-เกณฑ์การยอมรับ (Acceptance Criteria):
-- Given ระบบเปิดใช้งานต่อเนื่อง When ตรวจสอบสถิติ Uptime Then ระบบต้องมีความพร้อมใช้งานไม่ต่ำกว่า 99.9% และไม่มี Downtime ที่ไม่คาดคิด</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>เครื่องมือ Load Testing ส่ง Request ต่อเนื่อง 24 ชั่วโมง</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>ระบบสามารถรองรับการทำงานได้ต่อเนื่องโดยมี Uptime &gt;= 99.9% และหากเกิดข้อผิดพลาด Service สามารถกู้คืนตัวเองได้อัตโนมัติ</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>NFR-REL-001</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="C17" s="34" t="inlineStr">
+        <is>
+          <t>Test Case Objective</t>
+        </is>
+      </c>
+      <c r="D17" s="34" t="inlineStr">
+        <is>
+          <t>Test Step</t>
+        </is>
+      </c>
+      <c r="E17" s="34" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="F17" s="34" t="inlineStr">
+        <is>
+          <t>Test Type</t>
+        </is>
+      </c>
+      <c r="G17" s="34" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="H17" s="34" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="I17" s="34" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J17" s="34" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+      <c r="K17" s="34" t="inlineStr">
+        <is>
+          <t>Automate</t>
+        </is>
+      </c>
+      <c r="L17" s="34" t="inlineStr">
+        <is>
+          <t>Req No.</t>
+        </is>
+      </c>
+      <c r="M17" s="34" t="inlineStr">
+        <is>
+          <t>Platforms</t>
+        </is>
+      </c>
+      <c r="N17" s="34" t="inlineStr">
+        <is>
+          <t>Updated By</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="180" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>REQ-FALLBACK-001</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>ตรวจสอบตรรกะการแนะนำร้านอาหารและน้ำดื่มใกล้เคียง (Fallback Recommendation) กรณีระบบหลักหรือ NSW ล้มเหลวระหว่างรอการดำเนินการ</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="36" t="inlineStr">
         <is>
           <t>กลุ่มผู้ใช้ (Actor): ผู้ใช้งานระบบ (User)
 เงื่อนไขก่อนหน้า (Pre-conditions): ระบบ NSW หรือระบบหลักเกิดความล่าช้าหรือล้มเหลว (Downtime)
@@ -1155,46 +1269,76 @@
 - Given ระบบหลักหรือ NSW ล้มเหลว When ผู้ใช้รอหน้าจอนานเกินกำหนด Then ระบบแสดง Fallback Recommendation แนะนำร้านอาหารตาม Bayesian Popularity Score อย่างถูกต้องตามข้อกำหนด</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>จำลองสถานะ NSW API Timeout (504 Gateway Timeout), พิกัดที่ตั้งจำลองของผู้ใช้</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="36" t="inlineStr">
         <is>
           <t>ระบบแสดงหน้าจอแจ้งเตือนข้อผิดพลาดอย่างสุภาพ พร้อมแสดงรายการแนะนำร้านอาหารและน้ำดื่มที่เรียงลำดับตามคะแนนความนิยม (Bayesian Popularity Score) หรือร้านที่ใกล้ที่สุดที่เปิดบริการสำเร็จ</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="35" t="inlineStr">
         <is>
           <t>[-]</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="36" t="inlineStr">
         <is>
           <t>[-]</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="36" t="inlineStr"/>
+      <c r="I18" s="35" t="inlineStr"/>
+      <c r="J18" s="36" t="inlineStr">
         <is>
           <t>REQ-FALLBACK-001</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
+      <c r="K18" s="35" t="inlineStr">
+        <is>
+          <t>AI AGENT</t>
+        </is>
+      </c>
+      <c r="L18" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M18" s="35" t="inlineStr">
+        <is>
+          <t>Web Application</t>
+        </is>
+      </c>
+      <c r="N18" s="35" t="inlineStr">
+        <is>
+          <t>ข้อมูลใบแจ้งหนี้ (Invoice): สินค้าที่รหัสพิกัดศุลกากร (HS Code) ไม่อยู่ในตาราง Permission_Goods</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="20">
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I12:M12"/>
+    <mergeCell ref="B1:N4"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="D10:F10"/>
     <mergeCell ref="G4:H4"/>
-    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="I10:M10"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="D6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
